--- a/output/pdf_financials_xlsx/GVR.xlsx
+++ b/output/pdf_financials_xlsx/GVR.xlsx
@@ -2000,13 +2000,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>1.73756</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.73756</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.752843</v>
       </c>
     </row>
     <row r="93">
@@ -3031,7 +3031,11 @@
           <t>Reserves (Note 6)</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E8" s="5" t="n">
         <v>1.73756</v>
       </c>

--- a/output/pdf_financials_xlsx/GVR.xlsx
+++ b/output/pdf_financials_xlsx/GVR.xlsx
@@ -630,10 +630,10 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.004529</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.001173</v>
       </c>
     </row>
     <row r="13">
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.420498</v>
+        <v>-0.425027</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.124515</v>
+        <v>-0.125688</v>
       </c>
     </row>
     <row r="28">
@@ -948,10 +948,10 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.420498</v>
+        <v>-0.425027</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.124515</v>
+        <v>-0.125688</v>
       </c>
     </row>
     <row r="30">
@@ -1030,13 +1030,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.365292</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.153931</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.058307</v>
       </c>
     </row>
     <row r="35">
@@ -1062,13 +1062,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.365292</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.153931</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.058307</v>
       </c>
     </row>
     <row r="37">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.365292</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.153931</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.058307</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -2847,7 +2847,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">

--- a/output/pdf_financials_xlsx/GVR.xlsx
+++ b/output/pdf_financials_xlsx/GVR.xlsx
@@ -1576,13 +1576,13 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.017</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.017</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="68">
